--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -116,12 +116,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
@@ -265,13 +265,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -762,42 +762,34 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2183</v>
+        <v>2194</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>36463</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K3" s="5" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>36463</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -841,7 +833,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -903,7 +895,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -965,7 +957,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1027,7 +1019,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1089,7 +1081,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1151,7 +1143,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1213,7 +1205,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1275,7 +1267,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1337,7 +1329,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1399,7 +1391,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1461,7 +1453,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1523,7 +1515,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1655,7 +1647,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1717,7 +1709,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1779,7 +1771,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1841,7 +1833,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1903,7 +1895,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1965,7 +1957,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2027,7 +2019,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2089,7 +2081,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2151,7 +2143,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2213,7 +2205,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2275,7 +2267,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2337,7 +2329,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2399,7 +2391,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2461,7 +2453,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2523,7 +2515,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2585,7 +2577,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2647,7 +2639,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2709,7 +2701,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2771,7 +2763,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2903,7 +2895,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2965,7 +2957,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3027,7 +3019,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3089,7 +3081,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3151,7 +3143,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3213,7 +3205,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3275,7 +3267,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3407,7 +3399,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3469,7 +3461,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3531,7 +3523,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3663,7 +3655,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3725,7 +3717,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3787,7 +3779,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3849,7 +3841,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3902,7 +3894,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3911,14 +3903,14 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
         <v>12471000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>19216</v>
+        <v>19186</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3929,7 +3921,7 @@
         <v>12471000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>19216</v>
+        <v>19186</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -3973,7 +3965,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4035,7 +4027,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4097,7 +4089,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4159,7 +4151,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4221,7 +4213,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4283,7 +4275,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4415,7 +4407,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4477,7 +4469,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4539,7 +4531,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4671,7 +4663,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4733,7 +4725,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4795,7 +4787,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4857,7 +4849,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4919,7 +4911,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4981,7 +4973,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5043,7 +5035,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5167,7 +5159,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5229,7 +5221,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5291,7 +5283,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5423,7 +5415,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5485,7 +5477,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5547,7 +5539,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5679,7 +5671,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5741,7 +5733,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5803,7 +5795,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5865,7 +5857,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5927,7 +5919,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5989,7 +5981,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6051,7 +6043,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6113,7 +6105,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6175,7 +6167,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6237,7 +6229,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6299,7 +6291,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6361,7 +6353,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6423,7 +6415,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6485,7 +6477,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6598,7 +6590,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6608,7 +6600,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6647,10 +6639,10 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2183呎 (4+房)
--
--
-(待售)</t>
+          <t>A | 2194呎 (4+房)
+$8000万
+$36,463/呎
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6663,28 +6655,28 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1046呎 (3房)
 $2350万
 $22,467/呎
-(24年-04月-04日)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
+(24年-04月-05日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 651呎 (2房)
 $1321万
 $20,288/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $2131万
 $23,572/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -6695,36 +6687,36 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 634呎 (2房)
 $1240万
 $19,552/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 651呎 (2房)
 $1310万
 $20,128/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $2110万
 $23,338/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $748万
 $19,726/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -6734,36 +6726,36 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 634呎 (2房)
 $1230万
 $19,397/呎
-(23年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+(23年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 651呎 (2房)
 $1300万
 $19,968/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $2077万
 $22,970/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $722万
 $19,037/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -6773,23 +6765,23 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 634呎 (2房)
 $1225万
 $19,320/呎
-(24年-06月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+(24年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 651呎 (2房)
 $1295万
 $19,888/呎
-(26年-03月-08日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 -
@@ -6797,12 +6789,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $719万
 $18,979/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -6812,36 +6804,36 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 634呎 (2房)
 $1269万
 $20,013/呎
-(23年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+(23年-10月-30日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 651呎 (2房)
 $1290万
 $19,809/呎
-(25年-08月-31日)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+(25年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $2044万
 $22,607/呎
-(25年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
+(25年-06月-18日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $771万
 $20,346/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -6851,36 +6843,36 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1217万
 $19,166/呎
-(23年-10月-16日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+(23年-10月-17日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 650呎 (2房)
 $1282万
 $19,730/呎
-(24年-12月-05日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+(24年-12月-06日)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $1931万
 $21,360/呎
-(23年-10月-19日)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
+(23年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $715万
 $18,867/呎
-(23年-10月-17日)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -6890,36 +6882,36 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1212万
 $19,090/呎
-(23年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+(23年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 650呎 (2房)
 $1377万
 $21,186/呎
-(26年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $2011万
 $22,250/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $734万
 $19,377/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -6929,36 +6921,36 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1207万
 $19,013/呎
-(23年-10月-16日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+(23年-10月-17日)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 650呎 (2房)
 $1272万
 $19,573/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $1995万
 $22,073/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $711万
 $18,754/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -6968,23 +6960,23 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1203万
 $18,938/呎
-(23年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+(23年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 650呎 (2房)
 $1267万
 $19,495/呎
-(25年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
+(25年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 -
@@ -6992,12 +6984,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $709万
 $18,698/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -7007,36 +6999,36 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+(24年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 650呎 (2房)
 $1262万
 $19,417/呎
-(24年-12月-11日)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
+(24年-12月-12日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 $1870万
 $20,689/呎
-(23年-10月-26日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
+(23年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $707万
 $18,643/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -7046,23 +7038,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-06月-27日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+(24年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 650呎 (2房)
 $1325万
 $20,388/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 -
@@ -7070,12 +7062,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $779万
 $20,566/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -7085,23 +7077,23 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1188万
 $18,713/呎
-(24年-04月-18日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+(24年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1252万
 $19,293/呎
-(24年-12月-02日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+(24年-12月-03日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 -
@@ -7109,12 +7101,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $702万
 $18,530/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -7124,36 +7116,36 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1184万
 $18,639/呎
-(23年-11月-12日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
+(23年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
 $1247万
-$19,216/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
+$19,186/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 905呎 (3房)
 $1918万
 $21,189/呎
-(25年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
+(25年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $700万
 $18,475/呎
-(23年-10月-16日)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -7163,36 +7155,36 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1179万
 $18,565/呎
-(24年-11月-17日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
+(24年-11月-18日)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1242万
 $19,139/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
+(26年-03月-03日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 905呎 (3房)
 $1902万
 $21,021/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $698万
 $18,421/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -7202,23 +7194,23 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1174万
 $18,490/呎
-(24年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
+(24年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1299万
 $20,016/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 905呎 (3房)
 -
@@ -7226,12 +7218,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $696万
 $18,364/呎
-(23年-11月-27日)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -7241,23 +7233,23 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1169万
 $18,417/呎
-(24年-12月-02日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
+(24年-12月-03日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1294万
 $19,936/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 905呎 (3房)
 -
@@ -7265,12 +7257,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $687万
 $18,128/呎
-(23年-10月-23日)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -7280,36 +7272,36 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1165万
 $18,344/呎
-(24年-11月-10日)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
+(24年-11月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1289万
 $19,857/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 905呎 (3房)
 $1857万
 $20,524/呎
-(25年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+(25年-01月-28日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $685万
 $18,073/呎
-(23年-10月-18日)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -7319,20 +7311,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(23年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
+(23年-10月-16日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -7343,12 +7335,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月-15日)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -7358,23 +7350,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(24年-12月-02日)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
+(24年-12月-03日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
+(26年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 -
@@ -7382,12 +7374,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月-19日)</t>
+(23年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -7397,23 +7389,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1151万
 $18,125/呎
-(23年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
+(23年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1273万
 $19,621/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
 -
@@ -7421,12 +7413,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $679万
 $17,913/呎
-(23年-10月-24日)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -7436,36 +7428,36 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1113万
 $17,528/呎
-(23年-10月-17日)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
+(23年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1173万
 $18,070/呎
-(25年-10月-23日)</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
+(25年-10月-24日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 905呎 (2房)
 $1730万
 $19,117/呎
-(25年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
+(25年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $664万
 $17,509/呎
-(23年-10月-17日)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -7475,36 +7467,36 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $1137万
 $17,900/呎
-(25年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
+(25年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1107万
 $17,060/呎
-(24年-10月-01日)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
+(24年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 905呎 (2房)
 $1619万
 $17,892/呎
-(25年-11月-02日)</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
+(25年-11月-03日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $626万
 $16,518/呎
-(23年-10月-17日)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -7514,36 +7506,36 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $999万
 $15,730/呎
-(23年-10月-17日)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
+(23年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 649呎 (2房)
 $1055万
 $16,254/呎
-(23年-10月-25日)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
+(23年-10月-26日)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 856呎 (2房)
 $1637万
 $19,129/呎
-(23年-10月-30日)</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
+(23年-10月-31日)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 379呎 (1房)
 $599万
 $15,799/呎
-(23年-10月-15日)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -3324,38 +3324,30 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>20620400</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>22810</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K44" s="5" t="n">
+        <v>20620400</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>22810</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -6590,7 +6582,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6600,7 +6592,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7046,12 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 904呎 (3房)
--
--
-(待售)</t>
+$2062万
+$22,810/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
